--- a/erp-server/erp-server-oms/src/main/resources/excel/b2csoExportError.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2csoExportError.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$AI$1:$AI$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$AJ$1:$AJ$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <r>
       <rPr>
@@ -331,6 +331,9 @@
     <t>收件人税号</t>
   </si>
   <si>
+    <t>IE号</t>
+  </si>
+  <si>
     <t>收件人地址1</t>
   </si>
   <si>
@@ -488,6 +491,9 @@
   </si>
   <si>
     <t>{.receiverTaxNo}</t>
+  </si>
+  <si>
+    <t>{.ieNo}</t>
   </si>
   <si>
     <t>{.firstAddress}</t>
@@ -1515,7 +1521,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="15.125" customWidth="1"/>
@@ -1532,20 +1538,20 @@
     <col min="20" max="24" width="20.625" customWidth="1"/>
     <col min="25" max="25" width="16.625" customWidth="1"/>
     <col min="26" max="26" width="12.625" customWidth="1"/>
-    <col min="27" max="27" width="19.625" customWidth="1"/>
-    <col min="28" max="28" width="15.625" customWidth="1"/>
-    <col min="29" max="29" width="26.125" customWidth="1"/>
-    <col min="30" max="30" width="15.625" customWidth="1"/>
-    <col min="31" max="32" width="17.25" customWidth="1"/>
-    <col min="33" max="33" width="15.625" customWidth="1"/>
-    <col min="34" max="34" width="15.75" customWidth="1"/>
-    <col min="35" max="36" width="20.625" customWidth="1"/>
-    <col min="37" max="37" width="15.625" customWidth="1"/>
-    <col min="38" max="38" width="22" customWidth="1"/>
-    <col min="39" max="39" width="40" customWidth="1"/>
+    <col min="27" max="28" width="19.625" customWidth="1"/>
+    <col min="29" max="29" width="15.625" customWidth="1"/>
+    <col min="30" max="30" width="26.125" customWidth="1"/>
+    <col min="31" max="31" width="15.625" customWidth="1"/>
+    <col min="32" max="33" width="17.25" customWidth="1"/>
+    <col min="34" max="34" width="15.625" customWidth="1"/>
+    <col min="35" max="35" width="15.75" customWidth="1"/>
+    <col min="36" max="37" width="20.625" customWidth="1"/>
+    <col min="38" max="38" width="15.625" customWidth="1"/>
+    <col min="39" max="39" width="22" customWidth="1"/>
+    <col min="40" max="40" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:35">
+    <row r="1" s="1" customFormat="1" spans="1:36">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1636,127 +1642,133 @@
       <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
       <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AG1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="20.25" customHeight="1" spans="1:35">
+    <row r="2" s="2" customFormat="1" ht="20.25" customHeight="1" spans="1:36">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2csoExportError.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2csoExportError.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -214,7 +214,7 @@
     <t>物流渠道</t>
   </si>
   <si>
-    <t>跟踪号</t>
+    <t>运单号</t>
   </si>
   <si>
     <t>包装尺寸(长*宽*高)</t>
